--- a/gpt.xlsx
+++ b/gpt.xlsx
@@ -473,7 +473,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Updated by GitHub Actions: 2026-09-12T11:24:03.507932Z</t>
+          <t>Updated by GitHub Actions: 2026-09-13T12:28:00.816569Z</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">

--- a/gpt.xlsx
+++ b/gpt.xlsx
@@ -473,7 +473,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Updated by GitHub Actions: 2026-09-13T12:28:00.816569Z</t>
+          <t>Updated by GitHub Actions: 2026-09-14T13:31:35.400057Z</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">

--- a/gpt.xlsx
+++ b/gpt.xlsx
@@ -473,7 +473,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Updated by GitHub Actions: 2026-09-14T13:31:35.400057Z</t>
+          <t>Updated by GitHub Actions: 2026-09-15T12:22:57.572039Z</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">

--- a/gpt.xlsx
+++ b/gpt.xlsx
@@ -473,7 +473,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Updated by GitHub Actions: 2026-09-15T12:22:57.572039Z</t>
+          <t>Updated by GitHub Actions: 2026-09-16T12:20:22.626658Z</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">

--- a/gpt.xlsx
+++ b/gpt.xlsx
@@ -473,7 +473,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Updated by GitHub Actions: 2026-09-16T12:20:22.626658Z</t>
+          <t>Updated by GitHub Actions: 2026-09-17T12:20:04.911780Z</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">

--- a/gpt.xlsx
+++ b/gpt.xlsx
@@ -473,7 +473,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Updated by GitHub Actions: 2026-09-17T12:20:04.911780Z</t>
+          <t>Updated by GitHub Actions: 2026-09-18T11:59:51.512991Z</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">

--- a/gpt.xlsx
+++ b/gpt.xlsx
@@ -473,7 +473,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Updated by GitHub Actions: 2026-09-18T11:59:51.512991Z</t>
+          <t>Updated by GitHub Actions: 2026-09-19T11:43:43.599542Z</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">

--- a/gpt.xlsx
+++ b/gpt.xlsx
@@ -473,7 +473,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Updated by GitHub Actions: 2026-09-19T11:43:43.599542Z</t>
+          <t>Updated by GitHub Actions: 2026-09-20T11:56:27.009445Z</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">

--- a/gpt.xlsx
+++ b/gpt.xlsx
@@ -473,7 +473,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Updated by GitHub Actions: 2026-09-20T11:56:27.009445Z</t>
+          <t>Updated by GitHub Actions: 2026-09-21T13:30:31.961496Z</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">

--- a/gpt.xlsx
+++ b/gpt.xlsx
@@ -473,7 +473,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Updated by GitHub Actions: 2026-09-21T13:30:31.961496Z</t>
+          <t>Updated by GitHub Actions: 2026-09-22T12:15:06.901898Z</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">

--- a/gpt.xlsx
+++ b/gpt.xlsx
@@ -473,7 +473,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Updated by GitHub Actions: 2026-09-22T12:15:06.901898Z</t>
+          <t>Updated by GitHub Actions: 2026-09-23T12:27:57.342034Z</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">

--- a/gpt.xlsx
+++ b/gpt.xlsx
@@ -473,7 +473,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Updated by GitHub Actions: 2026-09-23T12:27:57.342034Z</t>
+          <t>Updated by GitHub Actions: 2026-09-24T12:27:42.083522Z</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">

--- a/gpt.xlsx
+++ b/gpt.xlsx
@@ -473,7 +473,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Updated by GitHub Actions: 2026-09-24T12:27:42.083522Z</t>
+          <t>Updated by GitHub Actions: 2026-09-25T12:28:28.574338Z</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">

--- a/gpt.xlsx
+++ b/gpt.xlsx
@@ -473,7 +473,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Updated by GitHub Actions: 2026-09-25T12:28:28.574338Z</t>
+          <t>Updated by GitHub Actions: 2026-09-26T11:59:03.327666Z</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">

--- a/gpt.xlsx
+++ b/gpt.xlsx
@@ -473,7 +473,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Updated by GitHub Actions: 2026-09-26T11:59:03.327666Z</t>
+          <t>Updated by GitHub Actions: 2026-09-27T12:36:34.151529Z</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">

--- a/gpt.xlsx
+++ b/gpt.xlsx
@@ -473,7 +473,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Updated by GitHub Actions: 2026-09-27T12:36:34.151529Z</t>
+          <t>Updated by GitHub Actions: 2026-09-28T14:47:23.114680Z</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">

--- a/gpt.xlsx
+++ b/gpt.xlsx
@@ -473,7 +473,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Updated by GitHub Actions: 2026-09-28T14:47:23.114680Z</t>
+          <t>Updated by GitHub Actions: 2026-09-29T13:36:48.448940Z</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">

--- a/gpt.xlsx
+++ b/gpt.xlsx
@@ -473,7 +473,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Updated by GitHub Actions: 2026-09-29T13:36:48.448940Z</t>
+          <t>Updated by GitHub Actions: 2026-09-30T13:12:58.385785Z</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">

--- a/gpt.xlsx
+++ b/gpt.xlsx
@@ -473,7 +473,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Updated by GitHub Actions: 2026-09-30T13:12:58.385785Z</t>
+          <t>Updated by GitHub Actions: 2026-10-01T14:03:50.766633Z</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">

--- a/gpt.xlsx
+++ b/gpt.xlsx
@@ -473,7 +473,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Updated by GitHub Actions: 2026-10-01T14:03:50.766633Z</t>
+          <t>Updated by GitHub Actions: 2026-10-02T13:23:51.752564Z</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">

--- a/gpt.xlsx
+++ b/gpt.xlsx
@@ -473,7 +473,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Updated by GitHub Actions: 2026-10-02T13:23:51.752564Z</t>
+          <t>Updated by GitHub Actions: 2026-10-03T12:09:41.589335Z</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">

--- a/gpt.xlsx
+++ b/gpt.xlsx
@@ -473,7 +473,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Updated by GitHub Actions: 2026-10-03T12:09:41.589335Z</t>
+          <t>Updated by GitHub Actions: 2026-10-04T12:59:40.936375Z</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">

--- a/gpt.xlsx
+++ b/gpt.xlsx
@@ -473,7 +473,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Updated by GitHub Actions: 2026-10-04T12:59:40.936375Z</t>
+          <t>Updated by GitHub Actions: 2026-10-05T15:26:30.402185Z</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">

--- a/gpt.xlsx
+++ b/gpt.xlsx
@@ -473,7 +473,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Updated by GitHub Actions: 2026-10-05T15:26:30.402185Z</t>
+          <t>Updated by GitHub Actions: 2026-10-06T13:49:02.076185Z</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">

--- a/gpt.xlsx
+++ b/gpt.xlsx
@@ -473,7 +473,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Updated by GitHub Actions: 2026-10-06T13:49:02.076185Z</t>
+          <t>Updated by GitHub Actions: 2026-10-07T14:06:30.256383Z</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">

--- a/gpt.xlsx
+++ b/gpt.xlsx
@@ -473,7 +473,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Updated by GitHub Actions: 2026-10-07T14:06:30.256383Z</t>
+          <t>Updated by GitHub Actions: 2026-10-08T14:16:51.152498Z</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">

--- a/gpt.xlsx
+++ b/gpt.xlsx
@@ -473,7 +473,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Updated by GitHub Actions: 2026-10-08T14:16:51.152498Z</t>
+          <t>Updated by GitHub Actions: 2026-10-09T14:01:42.162035Z</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">

--- a/gpt.xlsx
+++ b/gpt.xlsx
@@ -473,7 +473,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Updated by GitHub Actions: 2026-10-09T14:01:42.162035Z</t>
+          <t>Updated by GitHub Actions: 2026-10-10T13:10:34.079712Z</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">

--- a/gpt.xlsx
+++ b/gpt.xlsx
@@ -473,7 +473,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Updated by GitHub Actions: 2026-10-10T13:10:34.079712Z</t>
+          <t>Updated by GitHub Actions: 2026-10-11T13:41:04.265905Z</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">

--- a/gpt.xlsx
+++ b/gpt.xlsx
@@ -473,7 +473,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Updated by GitHub Actions: 2026-10-11T13:41:04.265905Z</t>
+          <t>Updated by GitHub Actions: 2026-10-12T16:21:54.351748Z</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">

--- a/gpt.xlsx
+++ b/gpt.xlsx
@@ -473,7 +473,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Updated by GitHub Actions: 2026-10-12T16:21:54.351748Z</t>
+          <t>Updated by GitHub Actions: 2026-10-13T14:42:44.603584Z</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">

--- a/gpt.xlsx
+++ b/gpt.xlsx
@@ -473,7 +473,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Updated by GitHub Actions: 2026-10-13T14:42:44.603584Z</t>
+          <t>Updated by GitHub Actions: 2026-10-14T12:34:38.882438Z</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">

--- a/gpt.xlsx
+++ b/gpt.xlsx
@@ -473,7 +473,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Updated by GitHub Actions: 2026-10-14T12:34:38.882438Z</t>
+          <t>Updated by GitHub Actions: 2026-10-15T12:21:05.732212Z</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">

--- a/gpt.xlsx
+++ b/gpt.xlsx
@@ -473,7 +473,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Updated by GitHub Actions: 2026-10-15T12:21:05.732212Z</t>
+          <t>Updated by GitHub Actions: 2026-10-16T12:01:12.328636Z</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">

--- a/gpt.xlsx
+++ b/gpt.xlsx
@@ -473,7 +473,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Updated by GitHub Actions: 2026-10-16T12:01:12.328636Z</t>
+          <t>Updated by GitHub Actions: 2026-10-17T11:17:02.410083Z</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">

--- a/gpt.xlsx
+++ b/gpt.xlsx
@@ -473,7 +473,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Updated by GitHub Actions: 2026-10-17T11:17:02.410083Z</t>
+          <t>Updated by GitHub Actions: 2026-10-18T11:53:15.122816Z</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">

--- a/gpt.xlsx
+++ b/gpt.xlsx
@@ -473,7 +473,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Updated by GitHub Actions: 2026-10-18T11:53:15.122816Z</t>
+          <t>Updated by GitHub Actions: 2026-10-19T14:12:28.969628Z</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">

--- a/gpt.xlsx
+++ b/gpt.xlsx
@@ -473,7 +473,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Updated by GitHub Actions: 2026-10-19T14:12:28.969628Z</t>
+          <t>Updated by GitHub Actions: 2026-10-20T12:26:54.275135Z</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">

--- a/gpt.xlsx
+++ b/gpt.xlsx
@@ -473,7 +473,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Updated by GitHub Actions: 2026-10-20T12:26:54.275135Z</t>
+          <t>Updated by GitHub Actions: 2026-10-21T12:36:40.459786Z</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">

--- a/gpt.xlsx
+++ b/gpt.xlsx
@@ -473,7 +473,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Updated by GitHub Actions: 2026-10-21T12:36:40.459786Z</t>
+          <t>Updated by GitHub Actions: 2026-10-22T12:40:57.728253Z</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">

--- a/gpt.xlsx
+++ b/gpt.xlsx
@@ -473,7 +473,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Updated by GitHub Actions: 2026-10-22T12:40:57.728253Z</t>
+          <t>Updated by GitHub Actions: 2026-10-23T12:18:45.248794Z</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">

--- a/gpt.xlsx
+++ b/gpt.xlsx
@@ -473,7 +473,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Updated by GitHub Actions: 2026-10-23T12:18:45.248794Z</t>
+          <t>Updated by GitHub Actions: 2026-10-24T11:45:18.827193Z</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">

--- a/gpt.xlsx
+++ b/gpt.xlsx
@@ -473,7 +473,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Updated by GitHub Actions: 2026-10-24T11:45:18.827193Z</t>
+          <t>Updated by GitHub Actions: 2026-10-25T12:14:39.429236Z</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">

--- a/gpt.xlsx
+++ b/gpt.xlsx
@@ -473,7 +473,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Updated by GitHub Actions: 2026-10-25T12:14:39.429236Z</t>
+          <t>Updated by GitHub Actions: 2026-10-26T13:45:46.052756Z</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">

--- a/gpt.xlsx
+++ b/gpt.xlsx
@@ -473,7 +473,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Updated by GitHub Actions: 2026-10-26T13:45:46.052756Z</t>
+          <t>Updated by GitHub Actions: 2026-10-27T12:53:19.141148Z</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">

--- a/gpt.xlsx
+++ b/gpt.xlsx
@@ -473,7 +473,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Updated by GitHub Actions: 2026-10-27T12:53:19.141148Z</t>
+          <t>Updated by GitHub Actions: 2026-10-28T13:41:10.367392Z</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">

--- a/gpt.xlsx
+++ b/gpt.xlsx
@@ -473,7 +473,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Updated by GitHub Actions: 2026-10-28T13:41:10.367392Z</t>
+          <t>Updated by GitHub Actions: 2026-10-29T13:51:44.265156Z</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">

--- a/gpt.xlsx
+++ b/gpt.xlsx
@@ -473,7 +473,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Updated by GitHub Actions: 2026-10-29T13:51:44.265156Z</t>
+          <t>Updated by GitHub Actions: 2026-10-30T13:44:05.949863Z</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">

--- a/gpt.xlsx
+++ b/gpt.xlsx
@@ -473,7 +473,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Updated by GitHub Actions: 2026-10-30T13:44:05.949863Z</t>
+          <t>Updated by GitHub Actions: 2026-10-31T13:13:04.076015Z</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
